--- a/feature-cb-ibd-ig/StructureDefinition-SIMDBC.xlsx
+++ b/feature-cb-ibd-ig/StructureDefinition-SIMDBC.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T14:27:57+00:00</t>
+    <t>2026-10-26T15:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-cb-ibd-ig/StructureDefinition-SIMDBC.xlsx
+++ b/feature-cb-ibd-ig/StructureDefinition-SIMDBC.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="215">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T15:58:19+00:00</t>
+    <t>2026-10-29T22:11:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Logisch model voor een DBC binnen het Santeon Informatiemodel.</t>
+    <t>Generiek logisch model voor een DBC binnen het Santeon Informatiemodel.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -231,10 +231,10 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: SIM CSVs</t>
-  </si>
-  <si>
-    <t>Mapping: SIM DBC naar FHIR</t>
+    <t>Mapping: SIM CSV</t>
+  </si>
+  <si>
+    <t>Mapping: SIMDBC naar FHIR</t>
   </si>
   <si>
     <t/>
@@ -253,86 +253,58 @@
     <t>Base</t>
   </si>
   <si>
-    <t>SIMDBC.Patient</t>
+    <t>SIMDBC.PatientIdentificatienummer</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ig.santeon.nl/sim-on-fhir/StructureDefinition/SIMPatient
-</t>
-  </si>
-  <si>
-    <t>Patiënt waarop de DBC betrekking heeft</t>
-  </si>
-  <si>
-    <t>Identificatienummer</t>
-  </si>
-  <si>
-    <t>EpisodeOfCare.patient</t>
-  </si>
-  <si>
-    <t>SIMDBC.SubtrajectNummer</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
+    <t>Identificatienummer van de patiënt</t>
+  </si>
+  <si>
+    <t>DBC;Identificatienummer</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.patient</t>
+  </si>
+  <si>
+    <t>SIMDBC.SubtrajectNummer</t>
+  </si>
+  <si>
     <t>Uniek identificatienummer van het DBC-subtraject</t>
   </si>
   <si>
-    <t>SubtrajectNr</t>
+    <t>DBC;SubtrajectNr</t>
   </si>
   <si>
     <t>EpisodeOfCare.identifier</t>
   </si>
   <si>
-    <t>SIMDBC.ZorgtrajectNummer</t>
-  </si>
-  <si>
-    <t>Identificatienummer van het zorgtraject</t>
-  </si>
-  <si>
-    <t>ZorgtrajectNr</t>
-  </si>
-  <si>
     <t>SIMDBC.Diagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Diagnose behorend bij de DBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>SIMDBC.Diagnose.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Diagnosecode en omschrijving</t>
-  </si>
-  <si>
-    <t>SIMDBC.SpecialismeDiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Specialisme en diagnose behorend bij de DBC</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://ig.santeon.nl/sim-on-fhir/ValueSet/Specialisme_DiagnoseCodelijstDummy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>EpisodeOfCare.diagnosis.condition</t>
-  </si>
-  <si>
-    <t>SIMDBC.SpecialismeDiagnose.id</t>
-  </si>
-  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -342,7 +314,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>SIMDBC.SpecialismeDiagnose.extension</t>
+    <t>SIMDBC.Diagnose.extension</t>
   </si>
   <si>
     <t>extensions
@@ -379,7 +351,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>SIMDBC.SpecialismeDiagnose.coding</t>
+    <t>SIMDBC.Diagnose.coding</t>
   </si>
   <si>
     <t>Y</t>
@@ -404,42 +376,72 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>SIMDBC.Diagnose.coding.code</t>
+  </si>
+  <si>
+    <t>DBC;DiagnoseCode</t>
+  </si>
+  <si>
+    <t>SIMDBC.Diagnose.coding.display</t>
+  </si>
+  <si>
+    <t>DBC;DiagnoseOmschrijving</t>
+  </si>
+  <si>
+    <t>SIMDBC.Diagnose.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>SIMDBC.SpecialismeDiagnose</t>
+  </si>
+  <si>
+    <t>Specialisme en diagnose behorend bij de DBC</t>
+  </si>
+  <si>
+    <t>SIMDBC.SpecialismeDiagnose.id</t>
+  </si>
+  <si>
+    <t>SIMDBC.SpecialismeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>SIMDBC.SpecialismeDiagnose.coding</t>
+  </si>
+  <si>
     <t>SIMDBC.SpecialismeDiagnose.coding.system</t>
   </si>
   <si>
-    <t>SpecialismeDiagnoseSysteem</t>
+    <t>DBC;SpecialismeDiagnoseSysteem</t>
   </si>
   <si>
     <t>SIMDBC.SpecialismeDiagnose.coding.code</t>
   </si>
   <si>
-    <t>SpecialismeDiagnoseCode</t>
+    <t>DBC;SpecialismeDiagnoseCode</t>
   </si>
   <si>
     <t>SIMDBC.SpecialismeDiagnose.coding.display</t>
   </si>
   <si>
-    <t>SpecialismeDiagnoseOmschrijving</t>
+    <t>DBC;SpecialismeDiagnoseOmschrijving</t>
   </si>
   <si>
     <t>SIMDBC.SpecialismeDiagnose.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
     <t>SIMDBC.ZorgType</t>
   </si>
   <si>
@@ -461,19 +463,19 @@
     <t>SIMDBC.ZorgType.coding.system</t>
   </si>
   <si>
-    <t>ZorgTypeCodeSysteem</t>
+    <t>DBC;ZorgTypeCodeSysteem</t>
   </si>
   <si>
     <t>SIMDBC.ZorgType.coding.code</t>
   </si>
   <si>
-    <t>ZorgTypeCode</t>
+    <t>DBC;ZorgTypeCode</t>
   </si>
   <si>
     <t>SIMDBC.ZorgType.coding.display</t>
   </si>
   <si>
-    <t>ZorgTypeOmschrijving</t>
+    <t>DBC;ZorgTypeOmschrijving</t>
   </si>
   <si>
     <t>SIMDBC.ZorgType.text</t>
@@ -497,19 +499,19 @@
     <t>SIMDBC.ZorgProduct.coding.system</t>
   </si>
   <si>
-    <t>ZorgProductCodeSysteem</t>
+    <t>DBC;ZorgProductCodeSysteem</t>
   </si>
   <si>
     <t>SIMDBC.ZorgProduct.coding.code</t>
   </si>
   <si>
-    <t>ZorgProductCode</t>
+    <t>DBC;ZorgProductCode</t>
   </si>
   <si>
     <t>SIMDBC.ZorgProduct.coding.display</t>
   </si>
   <si>
-    <t>ZorgProductOmschrijving</t>
+    <t>DBC;ZorgProductOmschrijving</t>
   </si>
   <si>
     <t>SIMDBC.ZorgProduct.text</t>
@@ -525,19 +527,16 @@
     <t>Geeft aan of de DBC verrichtingen bevat</t>
   </si>
   <si>
-    <t>DBCgevuld</t>
+    <t>DBC;DBCgevuld</t>
   </si>
   <si>
     <t>SIMDBC.Geldig</t>
   </si>
   <si>
-    <t>Geeft aan of de DBC geldig is</t>
-  </si>
-  <si>
-    <t>DBCgeldig</t>
-  </si>
-  <si>
-    <t>EpisodeOfCare.status</t>
+    <t>Geeft aan of de DBC administratief geldig is</t>
+  </si>
+  <si>
+    <t>DBC;DBCgeldig</t>
   </si>
   <si>
     <t>SIMDBC.OpeningsDatum</t>
@@ -550,7 +549,7 @@
     <t>Openingsdatum van de DBC</t>
   </si>
   <si>
-    <t>DBCOpeningsDatum</t>
+    <t>DBC;DBCOpeningsDatum</t>
   </si>
   <si>
     <t>EpisodeOfCare.period.start</t>
@@ -562,7 +561,7 @@
     <t>Sluitingsdatum van de DBC</t>
   </si>
   <si>
-    <t>DBCSluitingsDatum</t>
+    <t>DBC;DBCSluitingsDatum</t>
   </si>
   <si>
     <t>EpisodeOfCare.period.end</t>
@@ -602,7 +601,7 @@
     <t>Coding.system</t>
   </si>
   <si>
-    <t>Uitvoerder_SpecialismeSysteem</t>
+    <t>DBC;Uitvoerder_SpecialismeSysteem</t>
   </si>
   <si>
     <t>SIMDBC.UitvoerderSpecialisme.version</t>
@@ -639,7 +638,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>Uitvoerder_Specialisme</t>
+    <t>DBC;Uitvoerder_Specialisme</t>
   </si>
   <si>
     <t>SIMDBC.UitvoerderSpecialisme.display</t>
@@ -673,42 +672,6 @@
   </si>
   <si>
     <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer</t>
-  </si>
-  <si>
-    <t>Oorsprong van de verwijzing</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.id</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.extension</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.coding</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.coding.system</t>
-  </si>
-  <si>
-    <t>DBCverwijzerCodeSysteem</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.coding.code</t>
-  </si>
-  <si>
-    <t>DBCverwijzerCode</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.coding.display</t>
-  </si>
-  <si>
-    <t>DBCverwijzerCodeOmschrijving</t>
-  </si>
-  <si>
-    <t>SIMDBC.Verwijzer.text</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL50"/>
+  <dimension ref="A1:AL47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.30078125" customWidth="true" bestFit="true"/>
@@ -1023,7 +986,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.1328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1038,7 +1001,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.35546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1048,8 +1011,8 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="27.9921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.2265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="31.90625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="26.08203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1287,7 +1250,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>80</v>
@@ -1362,7 +1325,7 @@
         <v>79</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>80</v>
@@ -1408,13 +1371,13 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1480,18 +1443,18 @@
         <v>74</v>
       </c>
       <c r="AK4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL4" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AL4" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1514,7 +1477,7 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
         <v>91</v>
@@ -1571,7 +1534,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1583,10 +1546,10 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>74</v>
@@ -1626,7 +1589,7 @@
         <v>95</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1677,7 +1640,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
@@ -1700,21 +1663,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1726,15 +1689,17 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N7" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>74</v>
@@ -1759,55 +1724,57 @@
         <v>74</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y7" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z7" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>102</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1818,7 +1785,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1827,19 +1794,23 @@
         <v>74</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O8" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P8" t="s" s="2">
         <v>74</v>
       </c>
@@ -1887,19 +1858,19 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>74</v>
@@ -1910,22 +1881,20 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="G9" s="2"/>
       <c r="H9" t="s" s="2">
         <v>74</v>
       </c>
@@ -1936,17 +1905,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>74</v>
@@ -1983,34 +1946,32 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH9" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="AH9" s="2"/>
       <c r="AI9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>74</v>
@@ -2018,10 +1979,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2031,9 +1992,7 @@
       <c r="F10" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="G10" s="2"/>
       <c r="H10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2041,23 +2000,15 @@
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2105,22 +2056,20 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="AH10" s="2"/>
       <c r="AI10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2128,10 +2077,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2141,7 +2090,9 @@
       <c r="F11" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2149,15 +2100,23 @@
         <v>74</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2210,15 +2169,17 @@
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH11" s="2"/>
+      <c r="AH11" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>74</v>
@@ -2226,10 +2187,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2239,7 +2200,9 @@
       <c r="F12" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2250,10 +2213,14 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2303,20 +2270,22 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH12" s="2"/>
+      <c r="AH12" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>74</v>
@@ -2324,10 +2293,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2337,7 +2306,9 @@
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
       </c>
@@ -2348,10 +2319,14 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2401,12 +2376,14 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH13" s="2"/>
+      <c r="AH13" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI13" t="s" s="2">
         <v>74</v>
       </c>
@@ -2414,7 +2391,7 @@
         <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>74</v>
@@ -2422,21 +2399,21 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -2445,23 +2422,21 @@
         <v>74</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
@@ -2497,31 +2472,31 @@
         <v>74</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>74</v>
@@ -2532,10 +2507,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2546,7 +2521,7 @@
         <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>74</v>
@@ -2555,19 +2530,23 @@
         <v>74</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2615,33 +2594,33 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>140</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2651,9 +2630,7 @@
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G16" s="2"/>
       <c r="H16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2664,14 +2641,10 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2721,14 +2694,12 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH16" s="2"/>
       <c r="AI16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2736,7 +2707,7 @@
         <v>74</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>74</v>
@@ -2744,22 +2715,20 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="G17" s="2"/>
       <c r="H17" t="s" s="2">
         <v>74</v>
       </c>
@@ -2770,17 +2739,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -2817,34 +2780,32 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH17" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="AH17" s="2"/>
       <c r="AI17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -2852,10 +2813,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2865,9 +2826,7 @@
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G18" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="G18" s="2"/>
       <c r="H18" t="s" s="2">
         <v>74</v>
       </c>
@@ -2875,23 +2834,15 @@
         <v>74</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
       </c>
@@ -2939,22 +2890,20 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH18" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="AH18" s="2"/>
       <c r="AI18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>74</v>
@@ -2962,10 +2911,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2975,7 +2924,9 @@
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G19" s="2"/>
+      <c r="G19" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
       </c>
@@ -2983,15 +2934,23 @@
         <v>74</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
       </c>
@@ -3039,20 +2998,22 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH19" s="2"/>
+      <c r="AH19" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>74</v>
@@ -3060,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3073,7 +3034,9 @@
       <c r="F20" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G20" s="2"/>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
       </c>
@@ -3084,10 +3047,14 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3137,31 +3104,33 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH20" s="2"/>
+      <c r="AH20" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3171,7 +3140,9 @@
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G21" s="2"/>
+      <c r="G21" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
       </c>
@@ -3182,10 +3153,14 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3235,12 +3210,14 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH21" s="2"/>
+      <c r="AH21" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
       </c>
@@ -3248,7 +3225,7 @@
         <v>74</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
@@ -3256,21 +3233,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3279,23 +3256,21 @@
         <v>74</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
       </c>
@@ -3331,31 +3306,31 @@
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>74</v>
@@ -3366,10 +3341,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3380,7 +3355,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3389,19 +3364,23 @@
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
@@ -3449,19 +3428,19 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>74</v>
@@ -3472,10 +3451,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3485,9 +3464,7 @@
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G24" s="2"/>
       <c r="H24" t="s" s="2">
         <v>74</v>
       </c>
@@ -3498,14 +3475,10 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3555,14 +3528,12 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH24" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH24" s="2"/>
       <c r="AI24" t="s" s="2">
         <v>74</v>
       </c>
@@ -3570,7 +3541,7 @@
         <v>74</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
@@ -3578,22 +3549,20 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="G25" s="2"/>
       <c r="H25" t="s" s="2">
         <v>74</v>
       </c>
@@ -3604,17 +3573,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -3651,34 +3614,32 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH25" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="AH25" s="2"/>
       <c r="AI25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -3686,10 +3647,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3699,9 +3660,7 @@
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="G26" s="2"/>
       <c r="H26" t="s" s="2">
         <v>74</v>
       </c>
@@ -3709,23 +3668,15 @@
         <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
@@ -3773,22 +3724,20 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH26" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="AH26" s="2"/>
       <c r="AI26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>74</v>
@@ -3796,10 +3745,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3809,7 +3758,9 @@
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G27" s="2"/>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
       </c>
@@ -3817,15 +3768,23 @@
         <v>74</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>74</v>
       </c>
@@ -3873,20 +3832,22 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH27" s="2"/>
+      <c r="AH27" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>74</v>
@@ -3894,10 +3855,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3907,7 +3868,9 @@
       <c r="F28" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G28" s="2"/>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
       </c>
@@ -3918,10 +3881,14 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3971,20 +3938,22 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH28" s="2"/>
+      <c r="AH28" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>74</v>
@@ -3992,10 +3961,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4005,7 +3974,9 @@
       <c r="F29" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G29" s="2"/>
+      <c r="G29" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
       </c>
@@ -4016,10 +3987,14 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4069,12 +4044,14 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH29" s="2"/>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
       </c>
@@ -4082,7 +4059,7 @@
         <v>74</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>74</v>
@@ -4090,21 +4067,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
@@ -4113,23 +4090,21 @@
         <v>74</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
       </c>
@@ -4165,31 +4140,31 @@
         <v>74</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>74</v>
@@ -4200,10 +4175,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4214,7 +4189,7 @@
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
@@ -4223,19 +4198,23 @@
         <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>74</v>
       </c>
@@ -4283,22 +4262,22 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>74</v>
@@ -4306,10 +4285,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4319,9 +4298,7 @@
       <c r="F32" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G32" s="2"/>
       <c r="H32" t="s" s="2">
         <v>74</v>
       </c>
@@ -4332,14 +4309,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4389,14 +4362,12 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH32" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH32" s="2"/>
       <c r="AI32" t="s" s="2">
         <v>74</v>
       </c>
@@ -4404,18 +4375,18 @@
         <v>74</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>170</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4425,9 +4396,7 @@
       <c r="F33" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G33" s="2"/>
       <c r="H33" t="s" s="2">
         <v>74</v>
       </c>
@@ -4438,14 +4407,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4495,14 +4460,12 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH33" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH33" s="2"/>
       <c r="AI33" t="s" s="2">
         <v>74</v>
       </c>
@@ -4510,18 +4473,18 @@
         <v>74</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4531,9 +4494,7 @@
       <c r="F34" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G34" s="2"/>
       <c r="H34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4544,14 +4505,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4601,14 +4558,12 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH34" s="2"/>
       <c r="AI34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4616,18 +4571,18 @@
         <v>74</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4647,19 +4602,23 @@
         <v>74</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>74</v>
       </c>
@@ -4707,7 +4666,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -4719,7 +4678,7 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>74</v>
@@ -4730,10 +4689,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4756,13 +4715,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4813,7 +4772,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -4828,7 +4787,7 @@
         <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>74</v>
@@ -4836,21 +4795,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4862,17 +4821,15 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4909,34 +4866,34 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>74</v>
@@ -4944,10 +4901,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4967,23 +4924,19 @@
         <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5031,7 +4984,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5043,21 +4996,21 @@
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>74</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5077,20 +5030,18 @@
         <v>74</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5139,7 +5090,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -5151,21 +5102,21 @@
         <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>74</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5185,21 +5136,19 @@
         <v>74</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5247,7 +5196,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5259,10 +5208,10 @@
         <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>203</v>
+        <v>74</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>74</v>
@@ -5270,10 +5219,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5293,21 +5242,19 @@
         <v>74</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>206</v>
+        <v>96</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
       </c>
@@ -5355,7 +5302,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>97</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5367,7 +5314,7 @@
         <v>74</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>74</v>
@@ -5378,21 +5325,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -5401,23 +5348,21 @@
         <v>74</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5453,31 +5398,31 @@
         <v>74</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>74</v>
@@ -5488,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5511,19 +5456,23 @@
         <v>74</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -5571,7 +5520,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -5583,10 +5532,10 @@
         <v>74</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
@@ -5594,10 +5543,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5617,18 +5566,20 @@
         <v>74</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>94</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -5677,7 +5628,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -5689,7 +5640,7 @@
         <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>74</v>
@@ -5700,21 +5651,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5723,21 +5674,21 @@
         <v>74</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>110</v>
+        <v>199</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -5773,34 +5724,34 @@
         <v>74</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>74</v>
+        <v>203</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>74</v>
@@ -5808,10 +5759,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5822,7 +5773,7 @@
         <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
@@ -5831,22 +5782,20 @@
         <v>74</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
@@ -5895,19 +5844,19 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>74</v>
@@ -5918,10 +5867,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5931,7 +5880,9 @@
       <c r="F47" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G47" s="2"/>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
       </c>
@@ -5939,15 +5890,23 @@
         <v>74</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>74</v>
       </c>
@@ -5995,328 +5954,24 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH47" s="2"/>
+      <c r="AH47" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>221</v>
+        <v>74</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH48" s="2"/>
-      <c r="AI48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH49" s="2"/>
-      <c r="AI49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AL50" t="s" s="2">
         <v>74</v>
       </c>
     </row>
